--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
@@ -15589,7 +15589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población matriculada</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:37</t>
+    <t xml:space="preserve">2026-09-07 12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2019.xlsx
@@ -2134,7 +2134,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:55</t>
+    <t xml:space="preserve">2026-09-08 10:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
